--- a/files/UAE_005_ФФЗ.xlsx
+++ b/files/UAE_005_ФФЗ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zinov\OneDrive\Desktop\РАБОЧАЯ\001 ИМПОРТ\001 containers\2026\001 UAE\UAE#5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA60AF78-A571-4A9D-BADD-BF67DCE526D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4118A8E5-D060-4395-80BA-92AAB1C590BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="2040" windowWidth="35295" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ФПЗ_Э5" sheetId="1" r:id="rId1"/>
@@ -2060,15 +2060,15 @@
         <v>642.80379348003828</v>
       </c>
       <c r="V2" s="31">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="W2" s="32">
         <f>IFERROR((V2-U2)/U2,"")</f>
-        <v>0.24454772687156415</v>
+        <v>0.27566142004335326</v>
       </c>
       <c r="X2" s="33">
         <f t="shared" ref="X2:X9" si="7">V2*E2</f>
-        <v>9676800</v>
+        <v>9918720</v>
       </c>
       <c r="Y2" s="33">
         <f t="shared" ref="Y2:Y9" si="8">IFERROR(U2*E2,"")</f>
@@ -6396,15 +6396,15 @@
         <v>848.19331412929444</v>
       </c>
       <c r="V6" s="31">
-        <v>970</v>
+        <v>930</v>
       </c>
       <c r="W6" s="32">
         <f t="shared" si="16"/>
-        <v>0.1436072223650397</v>
+        <v>9.6448161648955602E-2</v>
       </c>
       <c r="X6" s="33">
         <f t="shared" si="7"/>
-        <v>5028480</v>
+        <v>4821120</v>
       </c>
       <c r="Y6" s="33">
         <f t="shared" si="8"/>
@@ -6714,7 +6714,7 @@
       <c r="W10" s="53"/>
       <c r="X10" s="63">
         <f>SUM(X2:X9)</f>
-        <v>22379040</v>
+        <v>22413600</v>
       </c>
       <c r="Y10" s="63">
         <f>SUM(Y2:Y9)</f>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="Y14" s="65">
         <f>(X10-Y10)/Y10</f>
-        <v>0.21848143096268466</v>
+        <v>0.22036313447874567</v>
       </c>
     </row>
     <row r="15" spans="1:1022" ht="15.75" x14ac:dyDescent="0.25">
